--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_30.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_30.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487E7669-7FBE-4C06-9A56-F38F5A7B17E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59312437-20EE-45EF-A140-88348ACAA221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="9972" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PayNowCCNoCF" sheetId="1" r:id="rId1"/>
     <sheet name="PayNowCCSCF" sheetId="2" r:id="rId2"/>
-    <sheet name="PayNowCCDCF" sheetId="3" r:id="rId3"/>
-    <sheet name="PayNowDCNoCF" sheetId="4" r:id="rId4"/>
-    <sheet name="CMCAutopayCC" sheetId="9" r:id="rId5"/>
-    <sheet name="PayNowDCSCF" sheetId="5" r:id="rId6"/>
-    <sheet name="PayNowDCDCF" sheetId="6" r:id="rId7"/>
-    <sheet name="CCDeferredCC" sheetId="7" r:id="rId8"/>
-    <sheet name="CCDeferredDC" sheetId="8" r:id="rId9"/>
-    <sheet name="NoModifyAmountCC" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId3"/>
+    <sheet name="PayNowCCDCF" sheetId="3" r:id="rId4"/>
+    <sheet name="PayNowDCNoCF" sheetId="4" r:id="rId5"/>
+    <sheet name="CMCAutopayCC" sheetId="9" r:id="rId6"/>
+    <sheet name="PayNowDCSCF" sheetId="5" r:id="rId7"/>
+    <sheet name="PayNowDCDCF" sheetId="6" r:id="rId8"/>
+    <sheet name="CCDeferredCC" sheetId="7" r:id="rId9"/>
+    <sheet name="CMCDeferredCC" sheetId="12" r:id="rId10"/>
+    <sheet name="CCDeferredDC" sheetId="8" r:id="rId11"/>
+    <sheet name="NoModifyAmountCC" sheetId="10" r:id="rId12"/>
+    <sheet name="NoModifyBillingAddressCC" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="47">
   <si>
     <t>Result</t>
   </si>
@@ -117,9 +120,6 @@
     <t>Tue May 26 20:16:10 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jun 01 21:44:26 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jun 01 21:46:04 IST 2026</t>
   </si>
   <si>
@@ -132,12 +132,6 @@
     <t>Tue Jun 16 19:59:04 IST 2026</t>
   </si>
   <si>
-    <t>Thu Jun 04 23:02:06 IST 2026</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
     <t>3.0</t>
   </si>
   <si>
@@ -156,19 +150,41 @@
     <t>6115</t>
   </si>
   <si>
-    <t>Thu Jul 16 20:40:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 16 21:18:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:16:47 IST 2026</t>
+    <t>12/31/2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 27 20:34:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 21:42:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 21:50:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 19:44:36 IST 2026</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 20:44:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:22:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:24:33 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -213,13 +229,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -548,11 +565,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>40</v>
+      <c r="B2" t="s" s="0">
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -561,13 +578,13 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
@@ -593,86 +610,377 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A09D3E-DDE8-4238-92BB-A14E037DF937}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3BD9EF-09CF-47C3-B934-D79A532B2550}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F914378-14C4-47D1-A6BA-2FC21D180B7D}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="6" style="4" width="8.88671875"/>
+    <col min="7" max="7" customWidth="true" style="4" width="25.6640625"/>
+    <col min="8" max="16384" style="4" width="8.88671875"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>15</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>6431</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4">
         <v>3</v>
       </c>
-      <c r="I2">
+      <c r="N2" s="4">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BE09F7-BAFF-4563-9A2F-E660A1FEC8FB}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" style="4" width="8.88671875"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J2">
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K2">
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4">
+        <v>6431</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="4">
         <v>3</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="4">
         <v>3</v>
       </c>
     </row>
@@ -731,24 +1039,24 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>41</v>
+      <c r="A2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>39</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>19</v>
@@ -760,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -776,6 +1084,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE968132-9731-448B-983E-0169F0D5D98C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D21E0C-5992-4DE0-8A6E-7444462EBA68}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -825,24 +1142,24 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>27</v>
+      <c r="B2" t="s" s="0">
+        <v>40</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>19</v>
@@ -854,7 +1171,7 @@
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -869,7 +1186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E1169B-5557-4267-8465-269061E22E67}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -919,11 +1236,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>28</v>
+      <c r="B2" t="s" s="0">
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>22</v>
@@ -932,13 +1249,13 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>19</v>
@@ -965,7 +1282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF89B9D8-B683-4E48-B73E-4AC43E364099}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1015,21 +1332,24 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="A2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>43</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>19</v>
@@ -1056,7 +1376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9D48FF-3EB3-4130-A9CE-771D994AFBC3}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1106,24 +1426,24 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
+      <c r="B2" t="s" s="0">
+        <v>28</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>19</v>
@@ -1150,7 +1470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59F2560-40CE-454F-A9CC-B5E3A656EC82}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1200,24 +1520,24 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>30</v>
+      <c r="B2" t="s" s="0">
+        <v>29</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>19</v>
@@ -1232,105 +1552,6 @@
         <v>24</v>
       </c>
       <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40ABC5F0-6A33-43C4-B16C-62020B0254E6}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
@@ -1344,9 +1565,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3BD9EF-09CF-47C3-B934-D79A532B2550}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40ABC5F0-6A33-43C4-B16C-62020B0254E6}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1392,27 +1616,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>19</v>
@@ -1424,7 +1646,7 @@
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>15</v>
@@ -1432,7 +1654,7 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
